--- a/phase-01/management/Журнал_задач.xlsx
+++ b/phase-01/management/Журнал_задач.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_C01CC778F1B409FF618E85DC6F102D09FEB88B0D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Журнал задач" sheetId="1" r:id="rId1"/>

--- a/phase-01/management/Журнал_задач.xlsx
+++ b/phase-01/management/Журнал_задач.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Works\VSU\ProjectManagment\phase-01\management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vlaud Detect\Desktop\ProjectManagment\phase-01\management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_C01CC778F1B409FF618E85DC6F102D09FEB88B0D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C4C8822-A266-48E7-8197-D9C5D7006610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Журнал задач" sheetId="1" r:id="rId1"/>
@@ -19,24 +19,11 @@
     <sheet name="История изменений" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="110">
   <si>
     <t>Сквозной журнал задач · план и факт</t>
   </si>
@@ -116,9 +103,6 @@
     <t>Участник 1</t>
   </si>
   <si>
-    <t>План</t>
-  </si>
-  <si>
     <t>Протокол встречи</t>
   </si>
   <si>
@@ -359,9 +343,6 @@
     <t>Редактор</t>
   </si>
   <si>
-    <t>v1.0 (черновик)</t>
-  </si>
-  <si>
     <t>Перенесены T01–T15 из исходной книги; плановые часы и сроки, факт не выдуман.</t>
   </si>
   <si>
@@ -369,6 +350,9 @@
   </si>
   <si>
     <t>Ожидает согласования</t>
+  </si>
+  <si>
+    <t>Выполнено</t>
   </si>
 </sst>
 </file>
@@ -379,7 +363,7 @@
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -399,10 +383,6 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -430,7 +410,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3D6"/>
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -443,39 +424,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -704,112 +683,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="33" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
     </row>
     <row r="3" spans="1:20" ht="36" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
-      <c r="J3" s="11"/>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
     </row>
     <row r="5" spans="1:20" ht="31.95" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="1" t="s">
+      <c r="J5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="K5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="P5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="Q5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="S5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="T5" s="1" t="s">
+      <c r="T5" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -826,43 +805,43 @@
       <c r="D6" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>46309</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>46309</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="4">
         <v>0.5</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="4">
         <v>0.5</v>
       </c>
-      <c r="I6" s="3">
+      <c r="I6" s="4">
         <v>0.5</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="4">
         <f t="shared" ref="J6:J20" si="0">SUM(G6:I6)</f>
         <v>1.5</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="3" t="str">
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="4" t="str">
         <f t="shared" ref="P6:P20" si="1">IF(COUNT(M6:O6)=0,"",SUM(M6:O6))</f>
         <v/>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="Q6" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="R6" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="R6" s="7" t="s">
-        <v>27</v>
       </c>
       <c r="S6" s="8"/>
       <c r="T6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -870,51 +849,51 @@
         <v>22</v>
       </c>
       <c r="B7" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>29</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>30</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>46309</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>46309</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="4">
         <v>1.4</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <v>0</v>
       </c>
-      <c r="I7" s="3">
+      <c r="I7" s="4">
         <v>0</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="4">
         <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="3" t="str">
+      <c r="K7" s="5"/>
+      <c r="L7" s="5"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q7" s="6" t="s">
-        <v>26</v>
+      <c r="Q7" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R7" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S7" s="8"/>
       <c r="T7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -922,51 +901,51 @@
         <v>22</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="E8" s="3">
         <v>46309</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>46309</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="4">
         <v>0</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="4">
         <v>1.4</v>
       </c>
-      <c r="I8" s="3">
+      <c r="I8" s="4">
         <v>0</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="4">
         <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="3" t="str">
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q8" s="6" t="s">
-        <v>26</v>
+      <c r="Q8" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="S8" s="8"/>
       <c r="T8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -974,51 +953,51 @@
         <v>22</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="E9" s="3">
         <v>46310</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>46310</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="4">
         <v>0.4</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="4">
         <v>0</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9" s="4">
         <v>1</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="4">
         <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="3" t="str">
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q9" s="6" t="s">
-        <v>26</v>
+      <c r="Q9" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R9" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="S9" s="8"/>
       <c r="T9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1026,51 +1005,51 @@
         <v>22</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="D10" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="2">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3">
         <v>46310</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>46310</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <v>0</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <v>0.4</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="4">
         <v>1</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="4">
         <f t="shared" si="0"/>
         <v>1.4</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="3" t="str">
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q10" s="6" t="s">
-        <v>26</v>
+      <c r="Q10" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R10" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="S10" s="8"/>
       <c r="T10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1078,51 +1057,51 @@
         <v>22</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="D11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="3">
         <v>46310</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>46310</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="4">
         <v>1.1000000000000001</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="4">
         <v>0.4</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I11" s="4">
         <v>0.4</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="4">
         <f t="shared" si="0"/>
         <v>1.9</v>
       </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="3" t="str">
+      <c r="K11" s="5"/>
+      <c r="L11" s="5"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q11" s="6" t="s">
-        <v>26</v>
+      <c r="Q11" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R11" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S11" s="8"/>
       <c r="T11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1130,51 +1109,51 @@
         <v>22</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="D12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="2">
+        <v>33</v>
+      </c>
+      <c r="E12" s="3">
         <v>46310</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>46311</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="4">
         <v>0.8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="4">
         <v>0.8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="4">
         <v>0.8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="4">
         <f t="shared" si="0"/>
         <v>2.4000000000000004</v>
       </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="3" t="str">
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q12" s="6" t="s">
-        <v>26</v>
+      <c r="Q12" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R12" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S12" s="8"/>
       <c r="T12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1182,51 +1161,51 @@
         <v>22</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="D13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E13" s="2">
+        <v>33</v>
+      </c>
+      <c r="E13" s="3">
         <v>46311</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>46312</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="4">
         <v>0.2</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="4">
         <v>0.3</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="4">
         <f t="shared" si="0"/>
         <v>2.7</v>
       </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="3" t="str">
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q13" s="6" t="s">
-        <v>26</v>
+      <c r="Q13" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S13" s="8"/>
       <c r="T13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1234,51 +1213,51 @@
         <v>22</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="D14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="2">
+        <v>37</v>
+      </c>
+      <c r="E14" s="3">
         <v>46311</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>46312</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="4">
         <v>1.2</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="4">
         <v>1.2</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="4">
         <v>1.2</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="4">
         <f t="shared" si="0"/>
         <v>3.5999999999999996</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="3" t="str">
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q14" s="6" t="s">
-        <v>26</v>
+      <c r="Q14" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1286,51 +1265,51 @@
         <v>22</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="D15" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="2">
+        <v>37</v>
+      </c>
+      <c r="E15" s="3">
         <v>46312</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>46313</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="4">
         <v>0.2</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="4">
         <v>0.3</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I15" s="4">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="4">
         <f t="shared" si="0"/>
         <v>2.8</v>
       </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="5"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="3" t="str">
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q15" s="6" t="s">
-        <v>26</v>
+      <c r="Q15" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1338,51 +1317,51 @@
         <v>22</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="D16" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="2">
+        <v>33</v>
+      </c>
+      <c r="E16" s="3">
         <v>46313</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>46313</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="4">
         <v>0.4</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="4">
         <v>0.9</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I16" s="4">
         <v>0.7</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="5"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="3" t="str">
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q16" s="6" t="s">
-        <v>26</v>
+      <c r="Q16" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1390,51 +1369,51 @@
         <v>22</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>62</v>
       </c>
       <c r="D17" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="3">
         <v>46313</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>46313</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="4">
         <v>0.5</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="4">
         <v>0.5</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I17" s="4">
         <v>0.5</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="4">
         <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="5"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="3" t="str">
+      <c r="K17" s="5"/>
+      <c r="L17" s="5"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q17" s="6" t="s">
-        <v>26</v>
+      <c r="Q17" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R17" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="S17" s="8"/>
       <c r="T17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1442,51 +1421,51 @@
         <v>22</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="7" t="s">
         <v>64</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>65</v>
       </c>
       <c r="D18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="3">
         <v>46313</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>46314</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="4">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="4">
         <v>0.4</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I18" s="4">
         <v>0.3</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="4">
         <f t="shared" si="0"/>
         <v>2.9</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="3" t="str">
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q18" s="6" t="s">
-        <v>26</v>
+      <c r="Q18" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R18" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S18" s="8"/>
       <c r="T18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1494,51 +1473,51 @@
         <v>22</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>68</v>
-      </c>
       <c r="D19" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="2">
+        <v>37</v>
+      </c>
+      <c r="E19" s="3">
         <v>46314</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>46314</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="4">
         <v>0.4</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="4">
         <v>0.6</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I19" s="4">
         <v>1</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="4">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="3" t="str">
+      <c r="K19" s="5"/>
+      <c r="L19" s="5"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q19" s="6" t="s">
-        <v>26</v>
+      <c r="Q19" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R19" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S19" s="8"/>
       <c r="T19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="37.950000000000003" customHeight="1">
@@ -1546,51 +1525,51 @@
         <v>22</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>71</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="3">
         <v>46314</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>46314</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="4">
         <v>0.4</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="4">
         <v>0</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I20" s="4">
         <v>0</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="4">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="3" t="str">
+      <c r="K20" s="5"/>
+      <c r="L20" s="5"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="4" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="Q20" s="6" t="s">
-        <v>26</v>
+      <c r="Q20" s="11" t="s">
+        <v>109</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S20" s="8"/>
       <c r="T20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1619,36 +1598,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="36" customHeight="1">
+      <c r="A3" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-    </row>
-    <row r="3" spans="1:6" ht="36" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+    </row>
+    <row r="5" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-    </row>
-    <row r="5" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="27" customHeight="1">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B6">
         <f>COUNTA('Журнал задач'!B6:B20)</f>
@@ -1659,7 +1638,7 @@
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <f>SUM('Журнал задач'!J6:J20)</f>
         <v>29.3</v>
       </c>
@@ -1668,41 +1647,41 @@
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="3" t="str">
+      <c r="B8" s="4" t="str">
         <f>IF(COUNT('Журнал задач'!M6:O20)=0,"",SUM('Журнал задач'!M6:O20))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:6" ht="27" customHeight="1">
       <c r="A9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="3">
+        <v>77</v>
+      </c>
+      <c r="B9" s="4">
         <f>SUM('Журнал задач'!G6:G20)</f>
         <v>9.7000000000000028</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="27" customHeight="1">
       <c r="A10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="3">
+        <v>78</v>
+      </c>
+      <c r="B10" s="4">
         <f>SUM('Журнал задач'!H6:H20)</f>
         <v>9.6</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="27" customHeight="1">
       <c r="A11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="3">
+        <v>79</v>
+      </c>
+      <c r="B11" s="4">
         <f>SUM('Журнал задач'!I6:I20)</f>
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="27" customHeight="1">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B12">
         <f>COUNTIF('Журнал задач'!Q6:Q20,"Готово")</f>
@@ -1711,27 +1690,27 @@
     </row>
     <row r="13" spans="1:6" ht="27" customHeight="1">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13">
         <f>COUNTIF('Журнал задач'!Q6:Q20,"План")</f>
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="36" customHeight="1">
+      <c r="A17" s="10" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="36" customHeight="1">
-      <c r="A17" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1754,85 +1733,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="26.4" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="3" spans="1:5" ht="28.8" customHeight="1">
+      <c r="A3" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-    </row>
-    <row r="3" spans="1:5" ht="28.8" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+    </row>
+    <row r="5" spans="1:5" ht="25.65" customHeight="1">
+      <c r="A5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-    </row>
-    <row r="5" spans="1:5" ht="25.65" customHeight="1">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="40.799999999999997" customHeight="1">
       <c r="A6" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>89</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="40.799999999999997" customHeight="1">
       <c r="A7" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>91</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="40.799999999999997" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="40.799999999999997" customHeight="1">
       <c r="A9" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="40.799999999999997" customHeight="1">
       <c r="A10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="40.799999999999997" customHeight="1">
       <c r="A11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="40.799999999999997" customHeight="1">
       <c r="A12" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>101</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1858,53 +1837,53 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="4" spans="1:6" ht="31.95" customHeight="1">
+      <c r="A4" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-    </row>
-    <row r="4" spans="1:6" ht="31.95" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="43.05" customHeight="1">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>46308</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>110</v>
       </c>
     </row>
   </sheetData>
